--- a/data-raw/data_input_defoliation.xlsx
+++ b/data-raw/data_input_defoliation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trotsiuk/Documents/Research/software/r3PG/data-raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{188C1FD1-F10D-A740-BA95-24B996E35CD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FF43C66-D51C-614A-BC71-E09B5D04E354}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33140" yWindow="500" windowWidth="43660" windowHeight="31500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10160" yWindow="500" windowWidth="43660" windowHeight="31500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="site" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="162">
   <si>
     <t>latitude</t>
   </si>
@@ -523,6 +523,9 @@
   <si>
     <t>prop_npp</t>
   </si>
+  <si>
+    <t>def_type</t>
+  </si>
 </sst>
 </file>
 
@@ -25061,10 +25064,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A88D5E7-4ED0-6C46-95F2-C0683DE408CB}">
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -25072,28 +25075,31 @@
         <v>25</v>
       </c>
       <c r="C1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D1" t="s">
         <v>155</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>156</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>157</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>26</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>158</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>159</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>153</v>
       </c>
@@ -25101,24 +25107,27 @@
         <v>70</v>
       </c>
       <c r="C2">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="D2">
         <v>0.5</v>
       </c>
       <c r="E2">
+        <v>0.5</v>
+      </c>
+      <c r="F2">
         <v>0.1</v>
       </c>
-      <c r="F2" s="2">
+      <c r="G2" s="2">
         <v>1</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>60</v>
       </c>
-      <c r="H2">
+      <c r="I2">
         <v>0.4</v>
       </c>
-      <c r="I2">
+      <c r="J2">
         <v>0.8</v>
       </c>
     </row>

--- a/data-raw/data_input_defoliation.xlsx
+++ b/data-raw/data_input_defoliation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trotsiuk/Documents/Research/software/r3PG/data-raw/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Forrester\Models\3-PG\thinning_defoliation_events\Rdata\data\revised_files_Vova\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FF43C66-D51C-614A-BC71-E09B5D04E354}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C5B5D91-A7C7-4A78-BF07-A3B545FB9A23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10160" yWindow="500" windowWidth="43660" windowHeight="31500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="site" sheetId="1" r:id="rId1"/>
@@ -39,12 +39,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="155">
   <si>
     <t>latitude</t>
-  </si>
-  <si>
-    <t>altitude</t>
   </si>
   <si>
     <t>soil_class</t>
@@ -317,12 +314,6 @@
     <t>aH</t>
   </si>
   <si>
-    <t>nHB</t>
-  </si>
-  <si>
-    <t>nHC</t>
-  </si>
-  <si>
     <t>aV</t>
   </si>
   <si>
@@ -338,31 +329,7 @@
     <t>aK</t>
   </si>
   <si>
-    <t>nKB</t>
-  </si>
-  <si>
-    <t>nKH</t>
-  </si>
-  <si>
-    <t>nKC</t>
-  </si>
-  <si>
-    <t>nKrh</t>
-  </si>
-  <si>
     <t>aHL</t>
-  </si>
-  <si>
-    <t>nHLB</t>
-  </si>
-  <si>
-    <t>nHLL</t>
-  </si>
-  <si>
-    <t>nHLC</t>
-  </si>
-  <si>
-    <t>nHLrh</t>
   </si>
   <si>
     <t>Qa</t>
@@ -422,51 +389,6 @@
     <t>DlocationC</t>
   </si>
   <si>
-    <t>wsscale0</t>
-  </si>
-  <si>
-    <t>wsscaleB</t>
-  </si>
-  <si>
-    <t>wsscalerh</t>
-  </si>
-  <si>
-    <t>wsscalet</t>
-  </si>
-  <si>
-    <t>wsscaleC</t>
-  </si>
-  <si>
-    <t>wsshape0</t>
-  </si>
-  <si>
-    <t>wsshapeB</t>
-  </si>
-  <si>
-    <t>wsshaperh</t>
-  </si>
-  <si>
-    <t>wsshapet</t>
-  </si>
-  <si>
-    <t>wsshapeC</t>
-  </si>
-  <si>
-    <t>wslocation0</t>
-  </si>
-  <si>
-    <t>wslocationB</t>
-  </si>
-  <si>
-    <t>wslocationrh</t>
-  </si>
-  <si>
-    <t>wslocationt</t>
-  </si>
-  <si>
-    <t>wslocationC</t>
-  </si>
-  <si>
     <t>1900-01</t>
   </si>
   <si>
@@ -488,15 +410,6 @@
     <t>betafPhys</t>
   </si>
   <si>
-    <t>lt_fN</t>
-  </si>
-  <si>
-    <t>lt_fT</t>
-  </si>
-  <si>
-    <t>lt_fPhys</t>
-  </si>
-  <si>
     <t>1850-01</t>
   </si>
   <si>
@@ -515,9 +428,6 @@
     <t>root_retained</t>
   </si>
   <si>
-    <t>t_recover</t>
-  </si>
-  <si>
     <t>prop_carbs</t>
   </si>
   <si>
@@ -525,6 +435,75 @@
   </si>
   <si>
     <t>def_type</t>
+  </si>
+  <si>
+    <t>elevation</t>
+  </si>
+  <si>
+    <t>lt_mod_mths</t>
+  </si>
+  <si>
+    <t>st_Power</t>
+  </si>
+  <si>
+    <t>st_Intercept</t>
+  </si>
+  <si>
+    <t>st_fN</t>
+  </si>
+  <si>
+    <t>st_fT</t>
+  </si>
+  <si>
+    <t>st_fPhys</t>
+  </si>
+  <si>
+    <t>biom_prop_retained</t>
+  </si>
+  <si>
+    <t>def_recover_t</t>
+  </si>
+  <si>
+    <t>gammaAPAR</t>
+  </si>
+  <si>
+    <t>Hd</t>
+  </si>
+  <si>
+    <t>nH1</t>
+  </si>
+  <si>
+    <t>nH2</t>
+  </si>
+  <si>
+    <t>nH3</t>
+  </si>
+  <si>
+    <t>nH4</t>
+  </si>
+  <si>
+    <t>nK1</t>
+  </si>
+  <si>
+    <t>nK2</t>
+  </si>
+  <si>
+    <t>nK3</t>
+  </si>
+  <si>
+    <t>nK4</t>
+  </si>
+  <si>
+    <t>nHL1</t>
+  </si>
+  <si>
+    <t>nHL2</t>
+  </si>
+  <si>
+    <t>nHL3</t>
+  </si>
+  <si>
+    <t>nHL4</t>
   </si>
 </sst>
 </file>
@@ -552,18 +531,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -578,9 +551,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -878,36 +850,72 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:T2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I1" t="s">
+        <v>133</v>
+      </c>
+      <c r="J1" t="s">
+        <v>134</v>
+      </c>
+      <c r="K1" t="s">
+        <v>135</v>
+      </c>
+      <c r="L1" t="s">
+        <v>136</v>
+      </c>
+      <c r="M1" t="s">
+        <v>137</v>
+      </c>
+      <c r="N1" t="s">
+        <v>138</v>
+      </c>
+      <c r="O1" t="s">
+        <v>117</v>
+      </c>
+      <c r="P1" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>119</v>
+      </c>
+      <c r="R1" t="s">
+        <v>120</v>
+      </c>
+      <c r="S1" t="s">
+        <v>121</v>
+      </c>
+      <c r="T1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>46.8609273677815</v>
       </c>
@@ -927,65 +935,96 @@
         <v>160.56756970000001</v>
       </c>
       <c r="G2" t="s">
-        <v>142</v>
+        <v>116</v>
       </c>
       <c r="H2" t="s">
-        <v>154</v>
+        <v>125</v>
+      </c>
+      <c r="I2">
+        <v>120</v>
+      </c>
+      <c r="J2">
+        <v>1.5</v>
+      </c>
+      <c r="K2">
+        <v>15</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>-15.9246784369849</v>
+      </c>
+      <c r="P2">
+        <v>1.0516235132282401</v>
+      </c>
+      <c r="Q2">
+        <v>2.1819192598143098</v>
+      </c>
+      <c r="R2">
+        <v>-1.3467926298486801</v>
+      </c>
+      <c r="S2">
+        <v>-1.5757229739474199</v>
+      </c>
+      <c r="T2">
+        <v>-2.1528301145871098</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Aptos"&amp;12&amp;KFF0000 OFFICIAL&amp;1#_x000D_</oddHeader>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;12&amp;KFF0000 OFFICIAL</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:K2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.83203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" t="s">
         <v>8</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>9</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>10</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>11</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>12</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>13</v>
       </c>
-      <c r="G1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>153</v>
+        <v>124</v>
       </c>
       <c r="B2" t="s">
-        <v>152</v>
+        <v>123</v>
       </c>
       <c r="C2">
         <v>0.6</v>
@@ -1002,62 +1041,56 @@
       <c r="G2">
         <v>3</v>
       </c>
-      <c r="H2" s="1">
-        <v>0.7</v>
-      </c>
-      <c r="I2" s="1">
-        <v>0.7</v>
-      </c>
-      <c r="J2" s="1">
-        <v>0.7</v>
-      </c>
-      <c r="K2" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Aptos"&amp;12&amp;KFF0000 OFFICIAL&amp;1#_x000D_</oddHeader>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;12&amp;KFF0000 OFFICIAL</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:J602"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" t="s">
         <v>15</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>16</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>17</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>18</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>19</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>20</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>21</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>22</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>23</v>
       </c>
-      <c r="J1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1900</v>
       </c>
@@ -1089,7 +1122,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1900</v>
       </c>
@@ -1121,7 +1154,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1900</v>
       </c>
@@ -1153,7 +1186,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>1900</v>
       </c>
@@ -1185,7 +1218,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>1900</v>
       </c>
@@ -1217,7 +1250,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>1900</v>
       </c>
@@ -1249,7 +1282,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>1900</v>
       </c>
@@ -1281,7 +1314,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>1900</v>
       </c>
@@ -1313,7 +1346,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>1900</v>
       </c>
@@ -1345,7 +1378,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>1900</v>
       </c>
@@ -1377,7 +1410,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>1900</v>
       </c>
@@ -1409,7 +1442,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>1900</v>
       </c>
@@ -1441,7 +1474,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>1901</v>
       </c>
@@ -1481,7 +1514,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>1901</v>
       </c>
@@ -1521,7 +1554,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>1901</v>
       </c>
@@ -1561,7 +1594,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>1901</v>
       </c>
@@ -1601,7 +1634,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>1901</v>
       </c>
@@ -1641,7 +1674,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>1901</v>
       </c>
@@ -1681,7 +1714,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>1901</v>
       </c>
@@ -1721,7 +1754,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>1901</v>
       </c>
@@ -1761,7 +1794,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>1901</v>
       </c>
@@ -1801,7 +1834,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>1901</v>
       </c>
@@ -1841,7 +1874,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>1901</v>
       </c>
@@ -1881,7 +1914,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>1901</v>
       </c>
@@ -1921,7 +1954,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>1902</v>
       </c>
@@ -1961,7 +1994,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>1902</v>
       </c>
@@ -2001,7 +2034,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>1902</v>
       </c>
@@ -2041,7 +2074,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>1902</v>
       </c>
@@ -2081,7 +2114,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>1902</v>
       </c>
@@ -2121,7 +2154,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>1902</v>
       </c>
@@ -2161,7 +2194,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>1902</v>
       </c>
@@ -2201,7 +2234,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>1902</v>
       </c>
@@ -2241,7 +2274,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>1902</v>
       </c>
@@ -2281,7 +2314,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>1902</v>
       </c>
@@ -2321,7 +2354,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>1902</v>
       </c>
@@ -2361,7 +2394,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>1902</v>
       </c>
@@ -2401,7 +2434,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>1903</v>
       </c>
@@ -2441,7 +2474,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>1903</v>
       </c>
@@ -2481,7 +2514,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>1903</v>
       </c>
@@ -2521,7 +2554,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>1903</v>
       </c>
@@ -2561,7 +2594,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>1903</v>
       </c>
@@ -2601,7 +2634,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>1903</v>
       </c>
@@ -2641,7 +2674,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>1903</v>
       </c>
@@ -2681,7 +2714,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>1903</v>
       </c>
@@ -2721,7 +2754,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>1903</v>
       </c>
@@ -2761,7 +2794,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>1903</v>
       </c>
@@ -2801,7 +2834,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>1903</v>
       </c>
@@ -2841,7 +2874,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>1903</v>
       </c>
@@ -2881,7 +2914,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>1904</v>
       </c>
@@ -2921,7 +2954,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>1904</v>
       </c>
@@ -2961,7 +2994,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>1904</v>
       </c>
@@ -3001,7 +3034,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>1904</v>
       </c>
@@ -3041,7 +3074,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>1904</v>
       </c>
@@ -3081,7 +3114,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>1904</v>
       </c>
@@ -3121,7 +3154,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>1904</v>
       </c>
@@ -3161,7 +3194,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>1904</v>
       </c>
@@ -3201,7 +3234,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>1904</v>
       </c>
@@ -3241,7 +3274,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>1904</v>
       </c>
@@ -3281,7 +3314,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>1904</v>
       </c>
@@ -3321,7 +3354,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>1904</v>
       </c>
@@ -3361,7 +3394,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>1905</v>
       </c>
@@ -3401,7 +3434,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>1905</v>
       </c>
@@ -3441,7 +3474,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>1905</v>
       </c>
@@ -3481,7 +3514,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>1905</v>
       </c>
@@ -3521,7 +3554,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>1905</v>
       </c>
@@ -3561,7 +3594,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>1905</v>
       </c>
@@ -3601,7 +3634,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>1905</v>
       </c>
@@ -3641,7 +3674,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>1905</v>
       </c>
@@ -3681,7 +3714,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>1905</v>
       </c>
@@ -3721,7 +3754,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>1905</v>
       </c>
@@ -3761,7 +3794,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>1905</v>
       </c>
@@ -3801,7 +3834,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>1905</v>
       </c>
@@ -3841,7 +3874,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>1906</v>
       </c>
@@ -3881,7 +3914,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>1906</v>
       </c>
@@ -3921,7 +3954,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>1906</v>
       </c>
@@ -3961,7 +3994,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>1906</v>
       </c>
@@ -4001,7 +4034,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>1906</v>
       </c>
@@ -4041,7 +4074,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>1906</v>
       </c>
@@ -4081,7 +4114,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>1906</v>
       </c>
@@ -4121,7 +4154,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>1906</v>
       </c>
@@ -4161,7 +4194,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>1906</v>
       </c>
@@ -4201,7 +4234,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>1906</v>
       </c>
@@ -4241,7 +4274,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>1906</v>
       </c>
@@ -4281,7 +4314,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>1906</v>
       </c>
@@ -4321,7 +4354,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>1907</v>
       </c>
@@ -4361,7 +4394,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>1907</v>
       </c>
@@ -4401,7 +4434,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>1907</v>
       </c>
@@ -4441,7 +4474,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>1907</v>
       </c>
@@ -4481,7 +4514,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>1907</v>
       </c>
@@ -4521,7 +4554,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>1907</v>
       </c>
@@ -4561,7 +4594,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>1907</v>
       </c>
@@ -4601,7 +4634,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>1907</v>
       </c>
@@ -4641,7 +4674,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>1907</v>
       </c>
@@ -4681,7 +4714,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>1907</v>
       </c>
@@ -4721,7 +4754,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>1907</v>
       </c>
@@ -4761,7 +4794,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>1907</v>
       </c>
@@ -4801,7 +4834,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>1908</v>
       </c>
@@ -4841,7 +4874,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>1908</v>
       </c>
@@ -4881,7 +4914,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>1908</v>
       </c>
@@ -4921,7 +4954,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>1908</v>
       </c>
@@ -4961,7 +4994,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>1908</v>
       </c>
@@ -5001,7 +5034,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>1908</v>
       </c>
@@ -5041,7 +5074,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>1908</v>
       </c>
@@ -5081,7 +5114,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>1908</v>
       </c>
@@ -5121,7 +5154,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>1908</v>
       </c>
@@ -5161,7 +5194,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>1908</v>
       </c>
@@ -5201,7 +5234,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>1908</v>
       </c>
@@ -5241,7 +5274,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>1908</v>
       </c>
@@ -5281,7 +5314,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>1909</v>
       </c>
@@ -5321,7 +5354,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>1909</v>
       </c>
@@ -5361,7 +5394,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>1909</v>
       </c>
@@ -5401,7 +5434,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>1909</v>
       </c>
@@ -5441,7 +5474,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>1909</v>
       </c>
@@ -5481,7 +5514,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>1909</v>
       </c>
@@ -5521,7 +5554,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>1909</v>
       </c>
@@ -5561,7 +5594,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>1909</v>
       </c>
@@ -5601,7 +5634,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>1909</v>
       </c>
@@ -5641,7 +5674,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>1909</v>
       </c>
@@ -5681,7 +5714,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>1909</v>
       </c>
@@ -5721,7 +5754,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>1909</v>
       </c>
@@ -5761,7 +5794,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>1910</v>
       </c>
@@ -5801,7 +5834,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>1910</v>
       </c>
@@ -5841,7 +5874,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>1910</v>
       </c>
@@ -5881,7 +5914,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>1910</v>
       </c>
@@ -5921,7 +5954,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>1910</v>
       </c>
@@ -5961,7 +5994,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>1910</v>
       </c>
@@ -6001,7 +6034,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>1910</v>
       </c>
@@ -6041,7 +6074,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>1910</v>
       </c>
@@ -6081,7 +6114,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>1910</v>
       </c>
@@ -6121,7 +6154,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>1910</v>
       </c>
@@ -6161,7 +6194,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>1910</v>
       </c>
@@ -6201,7 +6234,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>1910</v>
       </c>
@@ -6241,7 +6274,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>1911</v>
       </c>
@@ -6281,7 +6314,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>1911</v>
       </c>
@@ -6321,7 +6354,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>1911</v>
       </c>
@@ -6361,7 +6394,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>1911</v>
       </c>
@@ -6401,7 +6434,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>1911</v>
       </c>
@@ -6441,7 +6474,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>1911</v>
       </c>
@@ -6481,7 +6514,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>1911</v>
       </c>
@@ -6521,7 +6554,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>1911</v>
       </c>
@@ -6561,7 +6594,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>1911</v>
       </c>
@@ -6601,7 +6634,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>1911</v>
       </c>
@@ -6641,7 +6674,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>1911</v>
       </c>
@@ -6681,7 +6714,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="145" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>1911</v>
       </c>
@@ -6721,7 +6754,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="146" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>1912</v>
       </c>
@@ -6761,7 +6794,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="147" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>1912</v>
       </c>
@@ -6801,7 +6834,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="148" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>1912</v>
       </c>
@@ -6841,7 +6874,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="149" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>1912</v>
       </c>
@@ -6881,7 +6914,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="150" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>1912</v>
       </c>
@@ -6921,7 +6954,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="151" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>1912</v>
       </c>
@@ -6961,7 +6994,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="152" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>1912</v>
       </c>
@@ -7001,7 +7034,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="153" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>1912</v>
       </c>
@@ -7041,7 +7074,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="154" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>1912</v>
       </c>
@@ -7081,7 +7114,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="155" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>1912</v>
       </c>
@@ -7121,7 +7154,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="156" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>1912</v>
       </c>
@@ -7161,7 +7194,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="157" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>1912</v>
       </c>
@@ -7201,7 +7234,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="158" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>1913</v>
       </c>
@@ -7241,7 +7274,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="159" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>1913</v>
       </c>
@@ -7281,7 +7314,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="160" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>1913</v>
       </c>
@@ -7321,7 +7354,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="161" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>1913</v>
       </c>
@@ -7361,7 +7394,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="162" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>1913</v>
       </c>
@@ -7401,7 +7434,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="163" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>1913</v>
       </c>
@@ -7441,7 +7474,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="164" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>1913</v>
       </c>
@@ -7481,7 +7514,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="165" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>1913</v>
       </c>
@@ -7521,7 +7554,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="166" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>1913</v>
       </c>
@@ -7561,7 +7594,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="167" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>1913</v>
       </c>
@@ -7601,7 +7634,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="168" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>1913</v>
       </c>
@@ -7641,7 +7674,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="169" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>1913</v>
       </c>
@@ -7681,7 +7714,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="170" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>1914</v>
       </c>
@@ -7721,7 +7754,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="171" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>1914</v>
       </c>
@@ -7761,7 +7794,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="172" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>1914</v>
       </c>
@@ -7801,7 +7834,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="173" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>1914</v>
       </c>
@@ -7841,7 +7874,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="174" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>1914</v>
       </c>
@@ -7881,7 +7914,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="175" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>1914</v>
       </c>
@@ -7921,7 +7954,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="176" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>1914</v>
       </c>
@@ -7961,7 +7994,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="177" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>1914</v>
       </c>
@@ -8001,7 +8034,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="178" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>1914</v>
       </c>
@@ -8041,7 +8074,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="179" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>1914</v>
       </c>
@@ -8081,7 +8114,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="180" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>1914</v>
       </c>
@@ -8121,7 +8154,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="181" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>1914</v>
       </c>
@@ -8161,7 +8194,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="182" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>1915</v>
       </c>
@@ -8201,7 +8234,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="183" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>1915</v>
       </c>
@@ -8241,7 +8274,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="184" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>1915</v>
       </c>
@@ -8281,7 +8314,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="185" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>1915</v>
       </c>
@@ -8321,7 +8354,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="186" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>1915</v>
       </c>
@@ -8361,7 +8394,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="187" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>1915</v>
       </c>
@@ -8401,7 +8434,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="188" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>1915</v>
       </c>
@@ -8441,7 +8474,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="189" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>1915</v>
       </c>
@@ -8481,7 +8514,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="190" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>1915</v>
       </c>
@@ -8521,7 +8554,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="191" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>1915</v>
       </c>
@@ -8561,7 +8594,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="192" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>1915</v>
       </c>
@@ -8601,7 +8634,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="193" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>1915</v>
       </c>
@@ -8641,7 +8674,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="194" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>1916</v>
       </c>
@@ -8681,7 +8714,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="195" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>1916</v>
       </c>
@@ -8721,7 +8754,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="196" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>1916</v>
       </c>
@@ -8761,7 +8794,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="197" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>1916</v>
       </c>
@@ -8801,7 +8834,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="198" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>1916</v>
       </c>
@@ -8841,7 +8874,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="199" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>1916</v>
       </c>
@@ -8881,7 +8914,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="200" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>1916</v>
       </c>
@@ -8921,7 +8954,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="201" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>1916</v>
       </c>
@@ -8961,7 +8994,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="202" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A202">
         <v>1916</v>
       </c>
@@ -9001,7 +9034,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="203" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A203">
         <v>1916</v>
       </c>
@@ -9041,7 +9074,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="204" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A204">
         <v>1916</v>
       </c>
@@ -9081,7 +9114,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="205" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A205">
         <v>1916</v>
       </c>
@@ -9121,7 +9154,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="206" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A206">
         <v>1917</v>
       </c>
@@ -9161,7 +9194,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="207" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A207">
         <v>1917</v>
       </c>
@@ -9201,7 +9234,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="208" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A208">
         <v>1917</v>
       </c>
@@ -9241,7 +9274,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="209" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A209">
         <v>1917</v>
       </c>
@@ -9281,7 +9314,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="210" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A210">
         <v>1917</v>
       </c>
@@ -9321,7 +9354,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="211" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A211">
         <v>1917</v>
       </c>
@@ -9361,7 +9394,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="212" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A212">
         <v>1917</v>
       </c>
@@ -9401,7 +9434,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="213" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A213">
         <v>1917</v>
       </c>
@@ -9441,7 +9474,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="214" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A214">
         <v>1917</v>
       </c>
@@ -9481,7 +9514,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="215" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A215">
         <v>1917</v>
       </c>
@@ -9521,7 +9554,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="216" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A216">
         <v>1917</v>
       </c>
@@ -9561,7 +9594,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="217" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A217">
         <v>1917</v>
       </c>
@@ -9601,7 +9634,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="218" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A218">
         <v>1918</v>
       </c>
@@ -9641,7 +9674,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="219" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A219">
         <v>1918</v>
       </c>
@@ -9681,7 +9714,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="220" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A220">
         <v>1918</v>
       </c>
@@ -9721,7 +9754,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="221" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A221">
         <v>1918</v>
       </c>
@@ -9761,7 +9794,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="222" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A222">
         <v>1918</v>
       </c>
@@ -9801,7 +9834,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="223" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A223">
         <v>1918</v>
       </c>
@@ -9841,7 +9874,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="224" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A224">
         <v>1918</v>
       </c>
@@ -9881,7 +9914,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="225" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A225">
         <v>1918</v>
       </c>
@@ -9921,7 +9954,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="226" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A226">
         <v>1918</v>
       </c>
@@ -9961,7 +9994,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="227" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A227">
         <v>1918</v>
       </c>
@@ -10001,7 +10034,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="228" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A228">
         <v>1918</v>
       </c>
@@ -10041,7 +10074,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="229" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A229">
         <v>1918</v>
       </c>
@@ -10081,7 +10114,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="230" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A230">
         <v>1919</v>
       </c>
@@ -10121,7 +10154,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="231" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A231">
         <v>1919</v>
       </c>
@@ -10161,7 +10194,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="232" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A232">
         <v>1919</v>
       </c>
@@ -10201,7 +10234,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="233" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A233">
         <v>1919</v>
       </c>
@@ -10241,7 +10274,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="234" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A234">
         <v>1919</v>
       </c>
@@ -10281,7 +10314,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="235" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A235">
         <v>1919</v>
       </c>
@@ -10321,7 +10354,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="236" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A236">
         <v>1919</v>
       </c>
@@ -10361,7 +10394,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="237" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A237">
         <v>1919</v>
       </c>
@@ -10401,7 +10434,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="238" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A238">
         <v>1919</v>
       </c>
@@ -10441,7 +10474,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="239" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A239">
         <v>1919</v>
       </c>
@@ -10481,7 +10514,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="240" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A240">
         <v>1919</v>
       </c>
@@ -10521,7 +10554,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="241" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A241">
         <v>1919</v>
       </c>
@@ -10561,7 +10594,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="242" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A242">
         <v>1920</v>
       </c>
@@ -10601,7 +10634,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="243" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A243">
         <v>1920</v>
       </c>
@@ -10641,7 +10674,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="244" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A244">
         <v>1920</v>
       </c>
@@ -10681,7 +10714,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="245" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A245">
         <v>1920</v>
       </c>
@@ -10721,7 +10754,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="246" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A246">
         <v>1920</v>
       </c>
@@ -10761,7 +10794,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="247" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A247">
         <v>1920</v>
       </c>
@@ -10801,7 +10834,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="248" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A248">
         <v>1920</v>
       </c>
@@ -10841,7 +10874,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="249" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A249">
         <v>1920</v>
       </c>
@@ -10881,7 +10914,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="250" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A250">
         <v>1920</v>
       </c>
@@ -10921,7 +10954,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="251" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A251">
         <v>1920</v>
       </c>
@@ -10961,7 +10994,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="252" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A252">
         <v>1920</v>
       </c>
@@ -11001,7 +11034,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="253" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A253">
         <v>1920</v>
       </c>
@@ -11041,7 +11074,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="254" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A254">
         <v>1921</v>
       </c>
@@ -11081,7 +11114,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="255" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A255">
         <v>1921</v>
       </c>
@@ -11121,7 +11154,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="256" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A256">
         <v>1921</v>
       </c>
@@ -11161,7 +11194,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="257" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A257">
         <v>1921</v>
       </c>
@@ -11201,7 +11234,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="258" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A258">
         <v>1921</v>
       </c>
@@ -11241,7 +11274,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="259" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A259">
         <v>1921</v>
       </c>
@@ -11281,7 +11314,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="260" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A260">
         <v>1921</v>
       </c>
@@ -11321,7 +11354,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="261" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A261">
         <v>1921</v>
       </c>
@@ -11361,7 +11394,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="262" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A262">
         <v>1921</v>
       </c>
@@ -11401,7 +11434,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="263" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A263">
         <v>1921</v>
       </c>
@@ -11441,7 +11474,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="264" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A264">
         <v>1921</v>
       </c>
@@ -11481,7 +11514,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="265" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A265">
         <v>1921</v>
       </c>
@@ -11521,7 +11554,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="266" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A266">
         <v>1922</v>
       </c>
@@ -11561,7 +11594,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="267" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A267">
         <v>1922</v>
       </c>
@@ -11601,7 +11634,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="268" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A268">
         <v>1922</v>
       </c>
@@ -11641,7 +11674,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="269" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A269">
         <v>1922</v>
       </c>
@@ -11681,7 +11714,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="270" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A270">
         <v>1922</v>
       </c>
@@ -11721,7 +11754,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="271" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A271">
         <v>1922</v>
       </c>
@@ -11761,7 +11794,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="272" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A272">
         <v>1922</v>
       </c>
@@ -11801,7 +11834,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="273" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A273">
         <v>1922</v>
       </c>
@@ -11841,7 +11874,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="274" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A274">
         <v>1922</v>
       </c>
@@ -11881,7 +11914,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="275" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A275">
         <v>1922</v>
       </c>
@@ -11921,7 +11954,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="276" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A276">
         <v>1922</v>
       </c>
@@ -11961,7 +11994,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="277" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A277">
         <v>1922</v>
       </c>
@@ -12001,7 +12034,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="278" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A278">
         <v>1923</v>
       </c>
@@ -12041,7 +12074,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="279" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A279">
         <v>1923</v>
       </c>
@@ -12081,7 +12114,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="280" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A280">
         <v>1923</v>
       </c>
@@ -12121,7 +12154,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="281" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A281">
         <v>1923</v>
       </c>
@@ -12161,7 +12194,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="282" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A282">
         <v>1923</v>
       </c>
@@ -12201,7 +12234,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="283" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A283">
         <v>1923</v>
       </c>
@@ -12241,7 +12274,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="284" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A284">
         <v>1923</v>
       </c>
@@ -12281,7 +12314,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="285" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A285">
         <v>1923</v>
       </c>
@@ -12321,7 +12354,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="286" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A286">
         <v>1923</v>
       </c>
@@ -12361,7 +12394,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="287" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A287">
         <v>1923</v>
       </c>
@@ -12401,7 +12434,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="288" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A288">
         <v>1923</v>
       </c>
@@ -12441,7 +12474,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="289" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A289">
         <v>1923</v>
       </c>
@@ -12481,7 +12514,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="290" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A290">
         <v>1924</v>
       </c>
@@ -12521,7 +12554,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="291" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A291">
         <v>1924</v>
       </c>
@@ -12561,7 +12594,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="292" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A292">
         <v>1924</v>
       </c>
@@ -12601,7 +12634,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="293" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A293">
         <v>1924</v>
       </c>
@@ -12641,7 +12674,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="294" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A294">
         <v>1924</v>
       </c>
@@ -12681,7 +12714,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="295" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A295">
         <v>1924</v>
       </c>
@@ -12721,7 +12754,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="296" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A296">
         <v>1924</v>
       </c>
@@ -12761,7 +12794,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="297" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A297">
         <v>1924</v>
       </c>
@@ -12801,7 +12834,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="298" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A298">
         <v>1924</v>
       </c>
@@ -12841,7 +12874,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="299" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A299">
         <v>1924</v>
       </c>
@@ -12881,7 +12914,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="300" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A300">
         <v>1924</v>
       </c>
@@ -12921,7 +12954,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="301" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A301">
         <v>1924</v>
       </c>
@@ -12961,7 +12994,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="302" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A302">
         <v>1925</v>
       </c>
@@ -13001,7 +13034,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="303" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A303">
         <v>1925</v>
       </c>
@@ -13041,7 +13074,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="304" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A304">
         <v>1925</v>
       </c>
@@ -13081,7 +13114,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="305" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A305">
         <v>1925</v>
       </c>
@@ -13121,7 +13154,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="306" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A306">
         <v>1925</v>
       </c>
@@ -13161,7 +13194,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="307" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A307">
         <v>1925</v>
       </c>
@@ -13201,7 +13234,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="308" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A308">
         <v>1925</v>
       </c>
@@ -13241,7 +13274,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="309" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A309">
         <v>1925</v>
       </c>
@@ -13281,7 +13314,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="310" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A310">
         <v>1925</v>
       </c>
@@ -13321,7 +13354,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="311" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A311">
         <v>1925</v>
       </c>
@@ -13361,7 +13394,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="312" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A312">
         <v>1925</v>
       </c>
@@ -13401,7 +13434,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="313" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A313">
         <v>1925</v>
       </c>
@@ -13441,7 +13474,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="314" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A314">
         <v>1926</v>
       </c>
@@ -13481,7 +13514,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="315" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A315">
         <v>1926</v>
       </c>
@@ -13521,7 +13554,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="316" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A316">
         <v>1926</v>
       </c>
@@ -13561,7 +13594,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="317" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A317">
         <v>1926</v>
       </c>
@@ -13601,7 +13634,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="318" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A318">
         <v>1926</v>
       </c>
@@ -13641,7 +13674,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="319" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A319">
         <v>1926</v>
       </c>
@@ -13681,7 +13714,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="320" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A320">
         <v>1926</v>
       </c>
@@ -13721,7 +13754,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="321" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A321">
         <v>1926</v>
       </c>
@@ -13761,7 +13794,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="322" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A322">
         <v>1926</v>
       </c>
@@ -13801,7 +13834,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="323" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A323">
         <v>1926</v>
       </c>
@@ -13841,7 +13874,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="324" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A324">
         <v>1926</v>
       </c>
@@ -13881,7 +13914,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="325" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A325">
         <v>1926</v>
       </c>
@@ -13921,7 +13954,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="326" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A326">
         <v>1927</v>
       </c>
@@ -13961,7 +13994,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="327" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A327">
         <v>1927</v>
       </c>
@@ -14001,7 +14034,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="328" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A328">
         <v>1927</v>
       </c>
@@ -14041,7 +14074,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="329" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A329">
         <v>1927</v>
       </c>
@@ -14081,7 +14114,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="330" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A330">
         <v>1927</v>
       </c>
@@ -14121,7 +14154,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="331" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A331">
         <v>1927</v>
       </c>
@@ -14161,7 +14194,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="332" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A332">
         <v>1927</v>
       </c>
@@ -14201,7 +14234,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="333" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A333">
         <v>1927</v>
       </c>
@@ -14241,7 +14274,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="334" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A334">
         <v>1927</v>
       </c>
@@ -14281,7 +14314,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="335" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A335">
         <v>1927</v>
       </c>
@@ -14321,7 +14354,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="336" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A336">
         <v>1927</v>
       </c>
@@ -14361,7 +14394,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="337" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A337">
         <v>1927</v>
       </c>
@@ -14401,7 +14434,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="338" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A338">
         <v>1928</v>
       </c>
@@ -14441,7 +14474,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="339" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A339">
         <v>1928</v>
       </c>
@@ -14481,7 +14514,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="340" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A340">
         <v>1928</v>
       </c>
@@ -14521,7 +14554,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="341" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A341">
         <v>1928</v>
       </c>
@@ -14561,7 +14594,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="342" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A342">
         <v>1928</v>
       </c>
@@ -14601,7 +14634,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="343" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A343">
         <v>1928</v>
       </c>
@@ -14641,7 +14674,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="344" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A344">
         <v>1928</v>
       </c>
@@ -14681,7 +14714,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="345" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A345">
         <v>1928</v>
       </c>
@@ -14721,7 +14754,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="346" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A346">
         <v>1928</v>
       </c>
@@ -14761,7 +14794,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="347" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A347">
         <v>1928</v>
       </c>
@@ -14801,7 +14834,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="348" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A348">
         <v>1928</v>
       </c>
@@ -14841,7 +14874,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="349" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A349">
         <v>1928</v>
       </c>
@@ -14881,7 +14914,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="350" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A350">
         <v>1929</v>
       </c>
@@ -14921,7 +14954,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="351" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A351">
         <v>1929</v>
       </c>
@@ -14961,7 +14994,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="352" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A352">
         <v>1929</v>
       </c>
@@ -15001,7 +15034,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="353" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A353">
         <v>1929</v>
       </c>
@@ -15041,7 +15074,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="354" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A354">
         <v>1929</v>
       </c>
@@ -15081,7 +15114,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="355" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A355">
         <v>1929</v>
       </c>
@@ -15121,7 +15154,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="356" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A356">
         <v>1929</v>
       </c>
@@ -15161,7 +15194,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="357" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A357">
         <v>1929</v>
       </c>
@@ -15201,7 +15234,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="358" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A358">
         <v>1929</v>
       </c>
@@ -15241,7 +15274,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="359" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A359">
         <v>1929</v>
       </c>
@@ -15281,7 +15314,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="360" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A360">
         <v>1929</v>
       </c>
@@ -15321,7 +15354,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="361" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A361">
         <v>1929</v>
       </c>
@@ -15361,7 +15394,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="362" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A362">
         <v>1930</v>
       </c>
@@ -15401,7 +15434,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="363" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A363">
         <v>1930</v>
       </c>
@@ -15441,7 +15474,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="364" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A364">
         <v>1930</v>
       </c>
@@ -15481,7 +15514,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="365" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A365">
         <v>1930</v>
       </c>
@@ -15521,7 +15554,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="366" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A366">
         <v>1930</v>
       </c>
@@ -15561,7 +15594,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="367" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A367">
         <v>1930</v>
       </c>
@@ -15601,7 +15634,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="368" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A368">
         <v>1930</v>
       </c>
@@ -15641,7 +15674,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="369" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A369">
         <v>1930</v>
       </c>
@@ -15681,7 +15714,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="370" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A370">
         <v>1930</v>
       </c>
@@ -15721,7 +15754,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="371" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A371">
         <v>1930</v>
       </c>
@@ -15761,7 +15794,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="372" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A372">
         <v>1930</v>
       </c>
@@ -15801,7 +15834,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="373" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A373">
         <v>1930</v>
       </c>
@@ -15841,7 +15874,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="374" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A374">
         <v>1931</v>
       </c>
@@ -15881,7 +15914,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="375" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A375">
         <v>1931</v>
       </c>
@@ -15921,7 +15954,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="376" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A376">
         <v>1931</v>
       </c>
@@ -15961,7 +15994,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="377" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A377">
         <v>1931</v>
       </c>
@@ -16001,7 +16034,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="378" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A378">
         <v>1931</v>
       </c>
@@ -16041,7 +16074,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="379" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A379">
         <v>1931</v>
       </c>
@@ -16081,7 +16114,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="380" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A380">
         <v>1931</v>
       </c>
@@ -16121,7 +16154,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="381" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A381">
         <v>1931</v>
       </c>
@@ -16161,7 +16194,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="382" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A382">
         <v>1931</v>
       </c>
@@ -16201,7 +16234,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="383" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A383">
         <v>1931</v>
       </c>
@@ -16241,7 +16274,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="384" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A384">
         <v>1931</v>
       </c>
@@ -16281,7 +16314,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="385" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A385">
         <v>1931</v>
       </c>
@@ -16321,7 +16354,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="386" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A386">
         <v>1932</v>
       </c>
@@ -16361,7 +16394,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="387" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A387">
         <v>1932</v>
       </c>
@@ -16401,7 +16434,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="388" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A388">
         <v>1932</v>
       </c>
@@ -16441,7 +16474,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="389" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A389">
         <v>1932</v>
       </c>
@@ -16481,7 +16514,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="390" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A390">
         <v>1932</v>
       </c>
@@ -16521,7 +16554,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="391" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A391">
         <v>1932</v>
       </c>
@@ -16561,7 +16594,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="392" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A392">
         <v>1932</v>
       </c>
@@ -16601,7 +16634,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="393" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A393">
         <v>1932</v>
       </c>
@@ -16641,7 +16674,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="394" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A394">
         <v>1932</v>
       </c>
@@ -16681,7 +16714,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="395" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A395">
         <v>1932</v>
       </c>
@@ -16721,7 +16754,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="396" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A396">
         <v>1932</v>
       </c>
@@ -16761,7 +16794,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="397" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A397">
         <v>1932</v>
       </c>
@@ -16801,7 +16834,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="398" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A398">
         <v>1933</v>
       </c>
@@ -16841,7 +16874,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="399" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A399">
         <v>1933</v>
       </c>
@@ -16881,7 +16914,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="400" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A400">
         <v>1933</v>
       </c>
@@ -16921,7 +16954,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="401" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A401">
         <v>1933</v>
       </c>
@@ -16961,7 +16994,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="402" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A402">
         <v>1933</v>
       </c>
@@ -17001,7 +17034,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="403" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A403">
         <v>1933</v>
       </c>
@@ -17041,7 +17074,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="404" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A404">
         <v>1933</v>
       </c>
@@ -17081,7 +17114,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="405" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A405">
         <v>1933</v>
       </c>
@@ -17121,7 +17154,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="406" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A406">
         <v>1933</v>
       </c>
@@ -17161,7 +17194,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="407" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A407">
         <v>1933</v>
       </c>
@@ -17201,7 +17234,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="408" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A408">
         <v>1933</v>
       </c>
@@ -17241,7 +17274,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="409" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A409">
         <v>1933</v>
       </c>
@@ -17281,7 +17314,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="410" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A410">
         <v>1934</v>
       </c>
@@ -17321,7 +17354,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="411" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A411">
         <v>1934</v>
       </c>
@@ -17361,7 +17394,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="412" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A412">
         <v>1934</v>
       </c>
@@ -17401,7 +17434,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="413" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A413">
         <v>1934</v>
       </c>
@@ -17441,7 +17474,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="414" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A414">
         <v>1934</v>
       </c>
@@ -17481,7 +17514,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="415" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A415">
         <v>1934</v>
       </c>
@@ -17521,7 +17554,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="416" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A416">
         <v>1934</v>
       </c>
@@ -17561,7 +17594,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="417" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A417">
         <v>1934</v>
       </c>
@@ -17601,7 +17634,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="418" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A418">
         <v>1934</v>
       </c>
@@ -17641,7 +17674,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="419" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A419">
         <v>1934</v>
       </c>
@@ -17681,7 +17714,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="420" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A420">
         <v>1934</v>
       </c>
@@ -17721,7 +17754,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="421" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A421">
         <v>1934</v>
       </c>
@@ -17761,7 +17794,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="422" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A422">
         <v>1935</v>
       </c>
@@ -17801,7 +17834,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="423" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A423">
         <v>1935</v>
       </c>
@@ -17841,7 +17874,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="424" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A424">
         <v>1935</v>
       </c>
@@ -17881,7 +17914,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="425" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A425">
         <v>1935</v>
       </c>
@@ -17921,7 +17954,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="426" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A426">
         <v>1935</v>
       </c>
@@ -17961,7 +17994,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="427" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A427">
         <v>1935</v>
       </c>
@@ -18001,7 +18034,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="428" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A428">
         <v>1935</v>
       </c>
@@ -18041,7 +18074,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="429" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A429">
         <v>1935</v>
       </c>
@@ -18081,7 +18114,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="430" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A430">
         <v>1935</v>
       </c>
@@ -18121,7 +18154,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="431" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A431">
         <v>1935</v>
       </c>
@@ -18161,7 +18194,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="432" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A432">
         <v>1935</v>
       </c>
@@ -18201,7 +18234,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="433" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A433">
         <v>1935</v>
       </c>
@@ -18241,7 +18274,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="434" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A434">
         <v>1936</v>
       </c>
@@ -18281,7 +18314,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="435" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A435">
         <v>1936</v>
       </c>
@@ -18321,7 +18354,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="436" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A436">
         <v>1936</v>
       </c>
@@ -18361,7 +18394,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="437" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A437">
         <v>1936</v>
       </c>
@@ -18401,7 +18434,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="438" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A438">
         <v>1936</v>
       </c>
@@ -18441,7 +18474,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="439" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A439">
         <v>1936</v>
       </c>
@@ -18481,7 +18514,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="440" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A440">
         <v>1936</v>
       </c>
@@ -18521,7 +18554,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="441" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A441">
         <v>1936</v>
       </c>
@@ -18561,7 +18594,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="442" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A442">
         <v>1936</v>
       </c>
@@ -18601,7 +18634,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="443" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A443">
         <v>1936</v>
       </c>
@@ -18641,7 +18674,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="444" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A444">
         <v>1936</v>
       </c>
@@ -18681,7 +18714,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="445" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A445">
         <v>1936</v>
       </c>
@@ -18721,7 +18754,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="446" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A446">
         <v>1937</v>
       </c>
@@ -18761,7 +18794,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="447" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A447">
         <v>1937</v>
       </c>
@@ -18801,7 +18834,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="448" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A448">
         <v>1937</v>
       </c>
@@ -18841,7 +18874,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="449" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A449">
         <v>1937</v>
       </c>
@@ -18881,7 +18914,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="450" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A450">
         <v>1937</v>
       </c>
@@ -18921,7 +18954,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="451" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A451">
         <v>1937</v>
       </c>
@@ -18961,7 +18994,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="452" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A452">
         <v>1937</v>
       </c>
@@ -19001,7 +19034,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="453" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A453">
         <v>1937</v>
       </c>
@@ -19041,7 +19074,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="454" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A454">
         <v>1937</v>
       </c>
@@ -19081,7 +19114,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="455" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A455">
         <v>1937</v>
       </c>
@@ -19121,7 +19154,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="456" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A456">
         <v>1937</v>
       </c>
@@ -19161,7 +19194,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="457" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A457">
         <v>1937</v>
       </c>
@@ -19201,7 +19234,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="458" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A458">
         <v>1938</v>
       </c>
@@ -19241,7 +19274,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="459" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A459">
         <v>1938</v>
       </c>
@@ -19281,7 +19314,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="460" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A460">
         <v>1938</v>
       </c>
@@ -19321,7 +19354,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="461" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A461">
         <v>1938</v>
       </c>
@@ -19361,7 +19394,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="462" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A462">
         <v>1938</v>
       </c>
@@ -19401,7 +19434,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="463" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A463">
         <v>1938</v>
       </c>
@@ -19441,7 +19474,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="464" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A464">
         <v>1938</v>
       </c>
@@ -19481,7 +19514,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="465" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A465">
         <v>1938</v>
       </c>
@@ -19521,7 +19554,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="466" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A466">
         <v>1938</v>
       </c>
@@ -19561,7 +19594,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="467" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A467">
         <v>1938</v>
       </c>
@@ -19601,7 +19634,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="468" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A468">
         <v>1938</v>
       </c>
@@ -19641,7 +19674,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="469" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A469">
         <v>1938</v>
       </c>
@@ -19681,7 +19714,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="470" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A470">
         <v>1939</v>
       </c>
@@ -19721,7 +19754,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="471" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A471">
         <v>1939</v>
       </c>
@@ -19761,7 +19794,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="472" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A472">
         <v>1939</v>
       </c>
@@ -19801,7 +19834,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="473" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A473">
         <v>1939</v>
       </c>
@@ -19841,7 +19874,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="474" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A474">
         <v>1939</v>
       </c>
@@ -19881,7 +19914,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="475" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A475">
         <v>1939</v>
       </c>
@@ -19921,7 +19954,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="476" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A476">
         <v>1939</v>
       </c>
@@ -19961,7 +19994,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="477" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A477">
         <v>1939</v>
       </c>
@@ -20001,7 +20034,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="478" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A478">
         <v>1939</v>
       </c>
@@ -20041,7 +20074,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="479" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A479">
         <v>1939</v>
       </c>
@@ -20081,7 +20114,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="480" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A480">
         <v>1939</v>
       </c>
@@ -20121,7 +20154,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="481" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A481">
         <v>1939</v>
       </c>
@@ -20161,7 +20194,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="482" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A482">
         <v>1940</v>
       </c>
@@ -20201,7 +20234,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="483" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A483">
         <v>1940</v>
       </c>
@@ -20241,7 +20274,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="484" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A484">
         <v>1940</v>
       </c>
@@ -20281,7 +20314,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="485" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A485">
         <v>1940</v>
       </c>
@@ -20321,7 +20354,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="486" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A486">
         <v>1940</v>
       </c>
@@ -20361,7 +20394,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="487" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A487">
         <v>1940</v>
       </c>
@@ -20401,7 +20434,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="488" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A488">
         <v>1940</v>
       </c>
@@ -20441,7 +20474,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="489" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A489">
         <v>1940</v>
       </c>
@@ -20481,7 +20514,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="490" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A490">
         <v>1940</v>
       </c>
@@ -20521,7 +20554,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="491" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A491">
         <v>1940</v>
       </c>
@@ -20561,7 +20594,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="492" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A492">
         <v>1940</v>
       </c>
@@ -20601,7 +20634,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="493" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A493">
         <v>1940</v>
       </c>
@@ -20641,7 +20674,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="494" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A494">
         <v>1941</v>
       </c>
@@ -20681,7 +20714,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="495" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A495">
         <v>1941</v>
       </c>
@@ -20721,7 +20754,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="496" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A496">
         <v>1941</v>
       </c>
@@ -20761,7 +20794,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="497" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A497">
         <v>1941</v>
       </c>
@@ -20801,7 +20834,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="498" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A498">
         <v>1941</v>
       </c>
@@ -20841,7 +20874,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="499" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A499">
         <v>1941</v>
       </c>
@@ -20881,7 +20914,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="500" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A500">
         <v>1941</v>
       </c>
@@ -20921,7 +20954,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="501" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A501">
         <v>1941</v>
       </c>
@@ -20961,7 +20994,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="502" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A502">
         <v>1941</v>
       </c>
@@ -21001,7 +21034,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="503" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A503">
         <v>1941</v>
       </c>
@@ -21041,7 +21074,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="504" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A504">
         <v>1941</v>
       </c>
@@ -21081,7 +21114,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="505" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A505">
         <v>1941</v>
       </c>
@@ -21121,7 +21154,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="506" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A506">
         <v>1942</v>
       </c>
@@ -21161,7 +21194,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="507" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A507">
         <v>1942</v>
       </c>
@@ -21201,7 +21234,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="508" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A508">
         <v>1942</v>
       </c>
@@ -21241,7 +21274,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="509" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A509">
         <v>1942</v>
       </c>
@@ -21281,7 +21314,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="510" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A510">
         <v>1942</v>
       </c>
@@ -21321,7 +21354,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="511" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A511">
         <v>1942</v>
       </c>
@@ -21361,7 +21394,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="512" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A512">
         <v>1942</v>
       </c>
@@ -21401,7 +21434,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="513" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A513">
         <v>1942</v>
       </c>
@@ -21441,7 +21474,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="514" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A514">
         <v>1942</v>
       </c>
@@ -21481,7 +21514,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="515" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A515">
         <v>1942</v>
       </c>
@@ -21521,7 +21554,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="516" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A516">
         <v>1942</v>
       </c>
@@ -21561,7 +21594,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="517" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="517" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A517">
         <v>1942</v>
       </c>
@@ -21601,7 +21634,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="518" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="518" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A518">
         <v>1943</v>
       </c>
@@ -21641,7 +21674,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="519" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="519" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A519">
         <v>1943</v>
       </c>
@@ -21681,7 +21714,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="520" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="520" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A520">
         <v>1943</v>
       </c>
@@ -21721,7 +21754,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="521" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="521" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A521">
         <v>1943</v>
       </c>
@@ -21761,7 +21794,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="522" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="522" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A522">
         <v>1943</v>
       </c>
@@ -21801,7 +21834,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="523" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A523">
         <v>1943</v>
       </c>
@@ -21841,7 +21874,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="524" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="524" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A524">
         <v>1943</v>
       </c>
@@ -21881,7 +21914,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="525" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="525" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A525">
         <v>1943</v>
       </c>
@@ -21921,7 +21954,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="526" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="526" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A526">
         <v>1943</v>
       </c>
@@ -21961,7 +21994,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="527" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="527" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A527">
         <v>1943</v>
       </c>
@@ -22001,7 +22034,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="528" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="528" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A528">
         <v>1943</v>
       </c>
@@ -22041,7 +22074,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="529" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A529">
         <v>1943</v>
       </c>
@@ -22081,7 +22114,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="530" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="530" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A530">
         <v>1944</v>
       </c>
@@ -22121,7 +22154,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="531" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A531">
         <v>1944</v>
       </c>
@@ -22161,7 +22194,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="532" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A532">
         <v>1944</v>
       </c>
@@ -22201,7 +22234,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="533" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A533">
         <v>1944</v>
       </c>
@@ -22241,7 +22274,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="534" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A534">
         <v>1944</v>
       </c>
@@ -22281,7 +22314,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="535" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A535">
         <v>1944</v>
       </c>
@@ -22321,7 +22354,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="536" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A536">
         <v>1944</v>
       </c>
@@ -22361,7 +22394,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="537" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="537" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A537">
         <v>1944</v>
       </c>
@@ -22401,7 +22434,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="538" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="538" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A538">
         <v>1944</v>
       </c>
@@ -22441,7 +22474,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="539" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="539" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A539">
         <v>1944</v>
       </c>
@@ -22481,7 +22514,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="540" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="540" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A540">
         <v>1944</v>
       </c>
@@ -22521,7 +22554,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="541" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="541" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A541">
         <v>1944</v>
       </c>
@@ -22561,7 +22594,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="542" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="542" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A542">
         <v>1945</v>
       </c>
@@ -22601,7 +22634,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="543" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="543" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A543">
         <v>1945</v>
       </c>
@@ -22641,7 +22674,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="544" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="544" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A544">
         <v>1945</v>
       </c>
@@ -22681,7 +22714,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="545" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="545" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A545">
         <v>1945</v>
       </c>
@@ -22721,7 +22754,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="546" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="546" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A546">
         <v>1945</v>
       </c>
@@ -22761,7 +22794,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="547" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="547" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A547">
         <v>1945</v>
       </c>
@@ -22801,7 +22834,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="548" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="548" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A548">
         <v>1945</v>
       </c>
@@ -22841,7 +22874,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="549" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="549" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A549">
         <v>1945</v>
       </c>
@@ -22881,7 +22914,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="550" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="550" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A550">
         <v>1945</v>
       </c>
@@ -22921,7 +22954,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="551" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="551" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A551">
         <v>1945</v>
       </c>
@@ -22961,7 +22994,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="552" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="552" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A552">
         <v>1945</v>
       </c>
@@ -23001,7 +23034,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="553" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="553" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A553">
         <v>1945</v>
       </c>
@@ -23041,7 +23074,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="554" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="554" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A554">
         <v>1946</v>
       </c>
@@ -23081,7 +23114,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="555" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="555" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A555">
         <v>1946</v>
       </c>
@@ -23121,7 +23154,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="556" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="556" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A556">
         <v>1946</v>
       </c>
@@ -23161,7 +23194,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="557" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="557" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A557">
         <v>1946</v>
       </c>
@@ -23201,7 +23234,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="558" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="558" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A558">
         <v>1946</v>
       </c>
@@ -23241,7 +23274,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="559" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="559" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A559">
         <v>1946</v>
       </c>
@@ -23281,7 +23314,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="560" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="560" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A560">
         <v>1946</v>
       </c>
@@ -23321,7 +23354,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="561" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="561" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A561">
         <v>1946</v>
       </c>
@@ -23361,7 +23394,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="562" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="562" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A562">
         <v>1946</v>
       </c>
@@ -23401,7 +23434,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="563" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="563" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A563">
         <v>1946</v>
       </c>
@@ -23441,7 +23474,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="564" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="564" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A564">
         <v>1946</v>
       </c>
@@ -23481,7 +23514,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="565" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="565" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A565">
         <v>1946</v>
       </c>
@@ -23521,7 +23554,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="566" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="566" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A566">
         <v>1947</v>
       </c>
@@ -23561,7 +23594,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="567" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="567" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A567">
         <v>1947</v>
       </c>
@@ -23601,7 +23634,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="568" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="568" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A568">
         <v>1947</v>
       </c>
@@ -23641,7 +23674,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="569" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="569" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A569">
         <v>1947</v>
       </c>
@@ -23681,7 +23714,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="570" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="570" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A570">
         <v>1947</v>
       </c>
@@ -23721,7 +23754,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="571" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="571" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A571">
         <v>1947</v>
       </c>
@@ -23761,7 +23794,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="572" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="572" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A572">
         <v>1947</v>
       </c>
@@ -23801,7 +23834,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="573" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="573" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A573">
         <v>1947</v>
       </c>
@@ -23841,7 +23874,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="574" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="574" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A574">
         <v>1947</v>
       </c>
@@ -23881,7 +23914,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="575" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="575" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A575">
         <v>1947</v>
       </c>
@@ -23921,7 +23954,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="576" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="576" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A576">
         <v>1947</v>
       </c>
@@ -23961,7 +23994,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="577" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="577" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A577">
         <v>1947</v>
       </c>
@@ -24001,7 +24034,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="578" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="578" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A578">
         <v>1948</v>
       </c>
@@ -24041,7 +24074,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="579" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="579" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A579">
         <v>1948</v>
       </c>
@@ -24081,7 +24114,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="580" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="580" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A580">
         <v>1948</v>
       </c>
@@ -24121,7 +24154,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="581" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="581" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A581">
         <v>1948</v>
       </c>
@@ -24161,7 +24194,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="582" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="582" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A582">
         <v>1948</v>
       </c>
@@ -24201,7 +24234,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="583" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="583" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A583">
         <v>1948</v>
       </c>
@@ -24241,7 +24274,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="584" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="584" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A584">
         <v>1948</v>
       </c>
@@ -24281,7 +24314,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="585" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="585" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A585">
         <v>1948</v>
       </c>
@@ -24321,7 +24354,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="586" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="586" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A586">
         <v>1948</v>
       </c>
@@ -24361,7 +24394,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="587" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="587" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A587">
         <v>1948</v>
       </c>
@@ -24401,7 +24434,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="588" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="588" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A588">
         <v>1948</v>
       </c>
@@ -24441,7 +24474,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="589" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="589" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A589">
         <v>1948</v>
       </c>
@@ -24481,7 +24514,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="590" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="590" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A590">
         <v>1949</v>
       </c>
@@ -24521,7 +24554,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="591" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="591" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A591">
         <v>1949</v>
       </c>
@@ -24561,7 +24594,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="592" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="592" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A592">
         <v>1949</v>
       </c>
@@ -24601,7 +24634,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="593" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="593" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A593">
         <v>1949</v>
       </c>
@@ -24641,7 +24674,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="594" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="594" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A594">
         <v>1949</v>
       </c>
@@ -24681,7 +24714,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="595" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="595" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A595">
         <v>1949</v>
       </c>
@@ -24721,7 +24754,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="596" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="596" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A596">
         <v>1949</v>
       </c>
@@ -24761,7 +24794,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="597" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="597" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A597">
         <v>1949</v>
       </c>
@@ -24801,7 +24834,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="598" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="598" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A598">
         <v>1949</v>
       </c>
@@ -24841,7 +24874,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="599" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="599" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A599">
         <v>1949</v>
       </c>
@@ -24881,7 +24914,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="600" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="600" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A600">
         <v>1949</v>
       </c>
@@ -24921,7 +24954,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="601" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="601" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A601">
         <v>1949</v>
       </c>
@@ -24961,7 +24994,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="602" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="602" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A602">
         <v>1950</v>
       </c>
@@ -25004,40 +25037,47 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Aptos"&amp;12&amp;KFF0000 OFFICIAL&amp;1#_x000D_</oddHeader>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;12&amp;KFF0000 OFFICIAL</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" t="s">
         <v>25</v>
       </c>
-      <c r="C1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>26</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>27</v>
       </c>
-      <c r="F1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>153</v>
+        <v>124</v>
       </c>
       <c r="B2">
         <v>60</v>
@@ -25059,49 +25099,53 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Aptos"&amp;12&amp;KFF0000 OFFICIAL&amp;1#_x000D_</oddHeader>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;12&amp;KFF0000 OFFICIAL</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A88D5E7-4ED0-6C46-95F2-C0683DE408CB}">
   <dimension ref="A1:J2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" t="s">
+        <v>131</v>
+      </c>
+      <c r="D1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E1" t="s">
+        <v>127</v>
+      </c>
+      <c r="F1" t="s">
+        <v>128</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C1" t="s">
-        <v>161</v>
-      </c>
-      <c r="D1" t="s">
-        <v>155</v>
-      </c>
-      <c r="E1" t="s">
-        <v>156</v>
-      </c>
-      <c r="F1" t="s">
-        <v>157</v>
-      </c>
-      <c r="G1" t="s">
-        <v>26</v>
-      </c>
       <c r="H1" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
       <c r="I1" t="s">
-        <v>159</v>
+        <v>129</v>
       </c>
       <c r="J1" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>153</v>
+        <v>124</v>
       </c>
       <c r="B2">
         <v>70</v>
@@ -25118,7 +25162,7 @@
       <c r="F2">
         <v>0.1</v>
       </c>
-      <c r="G2" s="2">
+      <c r="G2" s="1">
         <v>1</v>
       </c>
       <c r="H2">
@@ -25133,726 +25177,714 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Aptos"&amp;12&amp;KFF0000 OFFICIAL&amp;1#_x000D_</oddHeader>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;12&amp;KFF0000 OFFICIAL</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:B89"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:B87"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>29</v>
-      </c>
-      <c r="B1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>30</v>
       </c>
       <c r="B2">
         <v>0.7</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B3">
         <v>0.3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B4">
         <v>0.13</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B5">
         <v>2.27</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B6">
         <v>0.7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B7">
         <v>0.3</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B8">
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B9">
         <v>1E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B10">
         <v>60</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B11">
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B12">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B13">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B14">
         <v>-5</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B15">
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B16">
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B17">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B18">
         <v>0.7</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B19">
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B20">
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B21">
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B22">
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B23">
         <v>0.2</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B24">
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B25">
         <v>350</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B26">
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B27">
         <v>0.95</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B28">
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B29">
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B30">
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B31">
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B32">
         <v>400</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B33">
         <v>1.5</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A34" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="B34" s="1">
-        <v>-15.9246784369849</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A35" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B35" s="1">
-        <v>1.0516235132282401</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A36" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="B36" s="1">
-        <v>2.1819192598143098</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A37" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="B37" s="1">
-        <v>-1.3467926298486801</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A38" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="B38" s="1">
-        <v>-1.5757229739474199</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A39" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="B39" s="1">
-        <v>-2.1528301145871098</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>61</v>
+      </c>
+      <c r="B34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>62</v>
+      </c>
+      <c r="B35">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>63</v>
+      </c>
+      <c r="B36">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>64</v>
+      </c>
+      <c r="B37">
+        <v>4.29</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>65</v>
+      </c>
+      <c r="B38">
+        <v>4.29</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>66</v>
+      </c>
+      <c r="B39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="B40">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B41" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A41" t="s">
-        <v>63</v>
-      </c>
-      <c r="B41">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>68</v>
+      </c>
+      <c r="B42">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>69</v>
+      </c>
+      <c r="B43">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>70</v>
+      </c>
+      <c r="B44">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>71</v>
+      </c>
+      <c r="B45">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>72</v>
+      </c>
+      <c r="B46">
+        <v>4.9000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>73</v>
+      </c>
+      <c r="B47">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>74</v>
+      </c>
+      <c r="B48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>75</v>
+      </c>
+      <c r="B49">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>76</v>
+      </c>
+      <c r="B50">
+        <v>3.33</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>77</v>
+      </c>
+      <c r="B51">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>78</v>
+      </c>
+      <c r="B52">
         <v>0.2</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A42" t="s">
-        <v>64</v>
-      </c>
-      <c r="B42">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A43" t="s">
-        <v>65</v>
-      </c>
-      <c r="B43">
-        <v>4.29</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
-        <v>66</v>
-      </c>
-      <c r="B44">
-        <v>4.29</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A45" t="s">
-        <v>67</v>
-      </c>
-      <c r="B45">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A46" t="s">
-        <v>68</v>
-      </c>
-      <c r="B46">
-        <v>0.38</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A47" t="s">
-        <v>69</v>
-      </c>
-      <c r="B47">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A48" t="s">
-        <v>70</v>
-      </c>
-      <c r="B48">
-        <v>0.39</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A49" t="s">
-        <v>71</v>
-      </c>
-      <c r="B49">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A50" t="s">
-        <v>72</v>
-      </c>
-      <c r="B50">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A51" t="s">
-        <v>73</v>
-      </c>
-      <c r="B51">
-        <v>4.9000000000000002E-2</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A52" t="s">
-        <v>74</v>
-      </c>
-      <c r="B52">
-        <v>0.47</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B53">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B54">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B55">
-        <v>3.33</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+        <v>4.4000000000000004</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B56">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B57">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B58">
-        <v>0.66</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B59">
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="B60">
-        <v>4.4000000000000004</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
+        <v>0.39500000000000002</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B61">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
+        <v>0.39500000000000002</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B62">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B63">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A64" t="s">
-        <v>86</v>
-      </c>
-      <c r="B64">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A65" t="s">
-        <v>87</v>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B64" s="1">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>90</v>
       </c>
       <c r="B65">
-        <v>0.39500000000000002</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A66" t="s">
-        <v>88</v>
+        <v>4.5890000000000004</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>143</v>
       </c>
       <c r="B66">
-        <v>0.39500000000000002</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A67" t="s">
-        <v>89</v>
+        <v>0.47399999999999998</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>144</v>
       </c>
       <c r="B67">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A68" t="s">
-        <v>90</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>145</v>
       </c>
       <c r="B68">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A69" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B69">
-        <v>4.5890000000000004</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A70" t="s">
+      <c r="B70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
         <v>92</v>
-      </c>
-      <c r="B70">
-        <v>0.47399999999999998</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A71" t="s">
-        <v>93</v>
       </c>
       <c r="B71">
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A72" t="s">
-        <v>94</v>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>93</v>
       </c>
       <c r="B72">
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A73" t="s">
-        <v>95</v>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
+        <v>94</v>
       </c>
       <c r="B73">
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A74" t="s">
-        <v>96</v>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
+        <v>95</v>
       </c>
       <c r="B74">
+        <v>1.3759999999999999</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B75">
+        <v>0.55400000000000005</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B76">
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A75" t="s">
-        <v>97</v>
-      </c>
-      <c r="B75">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A76" t="s">
-        <v>98</v>
-      </c>
-      <c r="B76">
-        <v>1.3759999999999999</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A77" t="s">
-        <v>99</v>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A77" s="1" t="s">
+        <v>149</v>
       </c>
       <c r="B77">
-        <v>0.55400000000000005</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A78" t="s">
-        <v>100</v>
+        <v>-0.27700000000000002</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A78" s="1" t="s">
+        <v>150</v>
       </c>
       <c r="B78">
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A79" t="s">
-        <v>101</v>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A79" s="1" t="s">
+        <v>96</v>
       </c>
       <c r="B79">
-        <v>-0.27700000000000002</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A80" t="s">
-        <v>102</v>
+        <v>2.1890000000000001</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A80" s="1" t="s">
+        <v>151</v>
       </c>
       <c r="B80">
+        <v>0.56299999999999994</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A81" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B81">
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A81" t="s">
-        <v>103</v>
-      </c>
-      <c r="B81">
-        <v>2.1890000000000001</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A82" t="s">
-        <v>104</v>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A82" s="1" t="s">
+        <v>153</v>
       </c>
       <c r="B82">
-        <v>0.56299999999999994</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A83" t="s">
-        <v>105</v>
+        <v>-0.26600000000000001</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A83" s="1" t="s">
+        <v>154</v>
       </c>
       <c r="B83">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A84" t="s">
-        <v>106</v>
+        <v>0.67800000000000005</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A84" s="1" t="s">
+        <v>97</v>
       </c>
       <c r="B84">
-        <v>-0.26600000000000001</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A85" t="s">
-        <v>107</v>
+        <v>-90</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A85" s="1" t="s">
+        <v>98</v>
       </c>
       <c r="B85">
-        <v>0.67800000000000005</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A86" t="s">
-        <v>108</v>
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A86" s="1" t="s">
+        <v>99</v>
       </c>
       <c r="B86">
-        <v>-90</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A87" t="s">
-        <v>109</v>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A87" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="B87">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A88" t="s">
-        <v>110</v>
-      </c>
-      <c r="B88">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A89" t="s">
-        <v>111</v>
-      </c>
-      <c r="B89">
         <v>2.2999999999999998</v>
       </c>
     </row>
@@ -25860,268 +25892,156 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Aptos"&amp;12&amp;KFF0000 OFFICIAL&amp;1#_x000D_</oddHeader>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;12&amp;KFF0000 OFFICIAL</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:B31"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:B16"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="B2">
         <v>0.27800000000000002</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="B3">
         <v>1.1519999999999999</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="B4">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="B5">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="B6">
         <v>5.3999999999999999E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="B7">
         <v>1.228</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="B8">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="B9">
         <v>1.1890000000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="B10">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="B11">
         <v>0.214</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="B12">
         <v>0.98699999999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="B13">
         <v>0.872</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="B14">
         <v>2.3E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="B15">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="B16">
         <v>-0.106</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>127</v>
-      </c>
-      <c r="B17">
-        <v>0.09</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>128</v>
-      </c>
-      <c r="B18">
-        <v>2.0840000000000001</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>129</v>
-      </c>
-      <c r="B19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>130</v>
-      </c>
-      <c r="B20">
-        <v>0.27100000000000002</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>131</v>
-      </c>
-      <c r="B21">
-        <v>-0.122</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>132</v>
-      </c>
-      <c r="B22">
-        <v>1.1339999999999999</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>133</v>
-      </c>
-      <c r="B23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>134</v>
-      </c>
-      <c r="B24">
-        <v>0.94499999999999995</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>135</v>
-      </c>
-      <c r="B25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>136</v>
-      </c>
-      <c r="B26">
-        <v>0.122</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>137</v>
-      </c>
-      <c r="B27">
-        <v>0.22800000000000001</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>138</v>
-      </c>
-      <c r="B28">
-        <v>2.2040000000000002</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>139</v>
-      </c>
-      <c r="B29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>140</v>
-      </c>
-      <c r="B30">
-        <v>-0.41899999999999998</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>141</v>
-      </c>
-      <c r="B31">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Aptos"&amp;12&amp;KFF0000 OFFICIAL&amp;1#_x000D_</oddHeader>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;12&amp;KFF0000 OFFICIAL</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
--- a/data-raw/data_input_defoliation.xlsx
+++ b/data-raw/data_input_defoliation.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Forrester\Models\3-PG\thinning_defoliation_events\Rdata\data\revised_files_Vova\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Forrester\Models\3-PG\r3PG_mortality_management_defoliation\data-raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C5B5D91-A7C7-4A78-BF07-A3B545FB9A23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFC239BB-073A-4A17-87CE-78ECD6F6FB86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="site" sheetId="1" r:id="rId1"/>
@@ -25083,7 +25083,7 @@
         <v>60</v>
       </c>
       <c r="C2">
-        <v>0.5</v>
+        <v>100</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -25157,10 +25157,10 @@
         <v>0.5</v>
       </c>
       <c r="E2">
+        <v>0.6</v>
+      </c>
+      <c r="F2">
         <v>0.5</v>
-      </c>
-      <c r="F2">
-        <v>0.1</v>
       </c>
       <c r="G2" s="1">
         <v>1</v>

--- a/data-raw/data_input_defoliation.xlsx
+++ b/data-raw/data_input_defoliation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Forrester\Models\3-PG\r3PG_mortality_management_defoliation\data-raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFC239BB-073A-4A17-87CE-78ECD6F6FB86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FD36B9A-C16D-4240-8337-104D4F3DC2AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
